--- a/projects/Sistema_financeiro/relatorio_financeiro.xlsx
+++ b/projects/Sistema_financeiro/relatorio_financeiro.xlsx
@@ -413,12 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -471,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02/06/2026 às 20:14</t>
+          <t>02/06/2026 às 20:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,17 +481,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Marketing - Consultoria SEO</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="E2" t="n">
-        <v>2400</v>
+        <v>280</v>
       </c>
       <c r="F2" t="n">
-        <v>7600</v>
+        <v>3220</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -499,37 +499,905 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02/06/2026 às 20:14</t>
+          <t>02/06/2026 às 20:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Vendas - Licença de Software PME</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E3" t="n">
+        <v>416</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4784</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Suporte - Contrato de Manutenção</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E4" t="n">
+        <v>384</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4416</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RH - Workshop de Capacitação</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>480</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5520</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Design - Criação de Identidade Visual</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>360</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4140</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TI - Desenvolvimento de App Mobile</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Marketing - Campanha de Tráfego Pago</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8900</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2136</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6764</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vendas - Lote de Equipamentos</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14200</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3408</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10792</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Infraestrutura - Migração para Nuvem</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2640</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8360</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Diretoria - Consultoria Estratégica</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11400</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Suporte - SLA Premium Mensal</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TI - Estruturação de Banco de Dados</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3120</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9880</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TI - Desenvolvimento de Software Enterprise</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>105000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>34650</v>
+      </c>
+      <c r="F14" t="n">
+        <v>70350</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Vendas - Contrato Anual de Distribuição</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>24750</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50250</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Marketing - Assessoria de Marca Anual</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>14850</v>
+      </c>
+      <c r="F16" t="n">
+        <v>30150</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Diretoria - Joint Venture / Parceria Comercial</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>39600</v>
+      </c>
+      <c r="F17" t="n">
+        <v>80400</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TI - Auditoria e Segurança de Sistemas</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>62000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>20460</v>
+      </c>
+      <c r="F18" t="n">
+        <v>41540</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Vendas - Renovação de Franquias</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>29040</v>
+      </c>
+      <c r="F19" t="n">
+        <v>58960</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Infraestrutura - Cabeamento Estruturado Predial</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>18150</v>
+      </c>
+      <c r="F20" t="n">
+        <v>36850</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TI - Implantação de IA e Analytics</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>13860</v>
+      </c>
+      <c r="F21" t="n">
+        <v>28140</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Despesa</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>despesa</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>-502</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>7098</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financeiro - Taxas Bancárias e Tarifa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RH - Folha de Pagamento Interna</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TI - Servidores AWS e Cloud Computing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>-8500</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marketing - Ferramentas de Automação e CRM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Administrativo - Aluguel do Escritório</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>-6800</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Jurídico - Honorários de Assessoria</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>-3500</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RH - Benefícios e Seguro Saúde</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>-4200</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TI - Licenças de Software (IDE, Office)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Vendas - Comissões da Equipe Comercial</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>-9300</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Operações - Fretes e Entregas</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>-5100</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Administrativo - Conta de Luz e Internet</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>-2200</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Marketing - Compra de Mídia Adwords/Meta</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Financeiro - Certificado Digital e Contador</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>-1800</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Suporte - Telefonia e Central de Atendimento</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>-3100</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>02/06/2026 às 20:54</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>RH - Compra de Cursos para Equipe</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>374116</v>
       </c>
     </row>
   </sheetData>
